--- a/local/agegroups/2026-Nationals.xlsx
+++ b/local/agegroups/2026-Nationals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/nemikor/usaw-owlcms/local/agegroups/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898DC0C6-0DF4-D74B-9B4F-115E16172D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288BED6D-637A-E446-BEDD-9AB414738E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1540" yWindow="660" windowWidth="33020" windowHeight="21680" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21880" yWindow="5240" windowWidth="33020" windowHeight="21680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AgeGroups" sheetId="1" r:id="rId1"/>
@@ -4342,10 +4342,16 @@
         <v>58</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N2">
         <v>2</v>
+      </c>
+      <c r="O2">
+        <v>5</v>
+      </c>
+      <c r="P2">
+        <v>5</v>
       </c>
       <c r="Q2" s="1"/>
       <c r="R2" t="b">
@@ -4387,10 +4393,16 @@
         <v>58</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N3">
         <v>2</v>
+      </c>
+      <c r="O3">
+        <v>5</v>
+      </c>
+      <c r="P3">
+        <v>5</v>
       </c>
       <c r="Q3" s="1"/>
       <c r="R3" t="b">
@@ -4432,10 +4444,16 @@
         <v>58</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N4">
         <v>2</v>
+      </c>
+      <c r="O4">
+        <v>5</v>
+      </c>
+      <c r="P4">
+        <v>5</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="R4" t="b">
@@ -4477,10 +4495,16 @@
         <v>58</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N5">
         <v>2</v>
+      </c>
+      <c r="O5">
+        <v>5</v>
+      </c>
+      <c r="P5">
+        <v>5</v>
       </c>
       <c r="Q5" s="6"/>
       <c r="R5" t="b">
@@ -4519,10 +4543,16 @@
         <v>23</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N6">
         <v>2</v>
+      </c>
+      <c r="O6">
+        <v>5</v>
+      </c>
+      <c r="P6">
+        <v>5</v>
       </c>
       <c r="Q6" s="6"/>
       <c r="R6" t="b">
@@ -4564,10 +4594,16 @@
         <v>58</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N7">
         <v>2</v>
+      </c>
+      <c r="O7">
+        <v>5</v>
+      </c>
+      <c r="P7">
+        <v>5</v>
       </c>
       <c r="Q7" s="1"/>
       <c r="R7" t="b">
@@ -4609,10 +4645,16 @@
         <v>58</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N8">
         <v>2</v>
+      </c>
+      <c r="O8">
+        <v>5</v>
+      </c>
+      <c r="P8">
+        <v>5</v>
       </c>
       <c r="Q8" s="6"/>
       <c r="R8" t="b">
@@ -4654,10 +4696,16 @@
         <v>58</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="N9">
         <v>2</v>
+      </c>
+      <c r="O9">
+        <v>5</v>
+      </c>
+      <c r="P9">
+        <v>5</v>
       </c>
       <c r="Q9" s="6"/>
       <c r="R9" t="b">

--- a/local/agegroups/2026-Nationals.xlsx
+++ b/local/agegroups/2026-Nationals.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/nemikor/usaw-owlcms/local/agegroups/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288BED6D-637A-E446-BEDD-9AB414738E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3E05F3-EB6D-FE42-98EB-0127D7A90223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21880" yWindow="5240" windowWidth="33020" windowHeight="21680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18980" yWindow="7540" windowWidth="33020" windowHeight="21680" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AgeGroups" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="99">
   <si>
     <t>code</t>
   </si>
@@ -4235,7 +4235,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32D632D4-A7F2-1446-BD59-BB7933F25245}">
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
@@ -4562,9 +4562,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A7" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>6</v>
@@ -4579,7 +4579,7 @@
         <v>57</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I7">
         <v>28</v>
@@ -4605,7 +4605,7 @@
       <c r="P7">
         <v>5</v>
       </c>
-      <c r="Q7" s="1"/>
+      <c r="Q7" s="6"/>
       <c r="R7" t="b">
         <v>0</v>
       </c>
@@ -4614,11 +4614,11 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A8" s="6" t="s">
-        <v>88</v>
+      <c r="A8" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
@@ -4630,7 +4630,7 @@
         <v>57</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I8">
         <v>28</v>
@@ -4661,57 +4661,6 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9">
-        <v>28</v>
-      </c>
-      <c r="J9">
-        <v>25</v>
-      </c>
-      <c r="K9">
-        <v>23</v>
-      </c>
-      <c r="L9" t="s">
-        <v>58</v>
-      </c>
-      <c r="M9">
-        <v>999</v>
-      </c>
-      <c r="N9">
-        <v>2</v>
-      </c>
-      <c r="O9">
-        <v>5</v>
-      </c>
-      <c r="P9">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="6"/>
-      <c r="R9" t="b">
-        <v>0</v>
-      </c>
-      <c r="S9">
         <v>5</v>
       </c>
     </row>
